--- a/js/jobs_data.xlsx
+++ b/js/jobs_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\B_Tech_CSE_Sem-6\ISC\NEW1\ISCwebsite2-main\ISCwebsite2-main\js\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\ISCwebsite2-main\ISCwebsite2-main\js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693EDABD-864A-4D9A-93F4-E8493B8CA0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A510B28-BCF7-4CB4-8136-B940BCC568FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>heading</t>
   </si>
@@ -32,45 +32,6 @@
   </si>
   <si>
     <t>Key Responsibilities</t>
-  </si>
-  <si>
-    <t>Assistant Manager - Electrical Design</t>
-  </si>
-  <si>
-    <t>Full-time | On-site</t>
-  </si>
-  <si>
-    <t>Experienced assistant manager role for electrical design.</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>Contract | On-site</t>
-  </si>
-  <si>
-    <t>Oversee project execution.</t>
-  </si>
-  <si>
-    <t>Data Analyst</t>
-  </si>
-  <si>
-    <t>Part-time | Remote</t>
-  </si>
-  <si>
-    <t>Analyze data sets.</t>
-  </si>
-  <si>
-    <t>HR Executive</t>
-  </si>
-  <si>
-    <t>Handles HR operations.</t>
-  </si>
-  <si>
-    <t>Manage recruitment process.</t>
-  </si>
-  <si>
-    <t>Lead electrical design projects.;other;other</t>
   </si>
 </sst>
 </file>
@@ -433,16 +394,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,62 +417,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
